--- a/artfynd/A 37200-2025 artfynd.xlsx
+++ b/artfynd/A 37200-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128345174</v>
       </c>
       <c r="B2" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>128345040</v>
       </c>
       <c r="B3" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>128345284</v>
       </c>
       <c r="B4" t="n">
-        <v>78789</v>
+        <v>78790</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>128345094</v>
       </c>
       <c r="B5" t="n">
-        <v>80134</v>
+        <v>80135</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>128345084</v>
       </c>
       <c r="B6" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128345052</v>
+        <v>128345220</v>
       </c>
       <c r="B7" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574628</v>
+        <v>574653</v>
       </c>
       <c r="R7" t="n">
-        <v>7088194</v>
+        <v>7088187</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1342,10 +1342,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128345220</v>
+        <v>128345052</v>
       </c>
       <c r="B8" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574653</v>
+        <v>574628</v>
       </c>
       <c r="R8" t="n">
-        <v>7088187</v>
+        <v>7088194</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1462,7 +1462,7 @@
         <v>128344999</v>
       </c>
       <c r="B9" t="n">
-        <v>92645</v>
+        <v>92650</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>128345013</v>
       </c>
       <c r="B10" t="n">
-        <v>78789</v>
+        <v>78790</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>128345290</v>
       </c>
       <c r="B11" t="n">
-        <v>91373</v>
+        <v>91378</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 37200-2025 artfynd.xlsx
+++ b/artfynd/A 37200-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128345174</v>
       </c>
       <c r="B2" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>128345040</v>
       </c>
       <c r="B3" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>128345284</v>
       </c>
       <c r="B4" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>128345094</v>
       </c>
       <c r="B5" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>128345084</v>
       </c>
       <c r="B6" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>128345220</v>
       </c>
       <c r="B7" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>128345052</v>
       </c>
       <c r="B8" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>128344999</v>
       </c>
       <c r="B9" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>128345013</v>
       </c>
       <c r="B10" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>128345290</v>
       </c>
       <c r="B11" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 37200-2025 artfynd.xlsx
+++ b/artfynd/A 37200-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128345174</v>
       </c>
       <c r="B2" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>128345040</v>
       </c>
       <c r="B3" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>128345284</v>
       </c>
       <c r="B4" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>128345094</v>
       </c>
       <c r="B5" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>128345084</v>
       </c>
       <c r="B6" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>128345220</v>
       </c>
       <c r="B7" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>128345052</v>
       </c>
       <c r="B8" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>128344999</v>
       </c>
       <c r="B9" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>128345013</v>
       </c>
       <c r="B10" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>128345290</v>
       </c>
       <c r="B11" t="n">
-        <v>91470</v>
+        <v>91482</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 37200-2025 artfynd.xlsx
+++ b/artfynd/A 37200-2025 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>128345284</v>
       </c>
       <c r="B4" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>128345094</v>
       </c>
       <c r="B5" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>128344999</v>
       </c>
       <c r="B9" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>128345013</v>
       </c>
       <c r="B10" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>128345290</v>
       </c>
       <c r="B11" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 37200-2025 artfynd.xlsx
+++ b/artfynd/A 37200-2025 artfynd.xlsx
@@ -1462,7 +1462,7 @@
         <v>128344999</v>
       </c>
       <c r="B9" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>128345290</v>
       </c>
       <c r="B11" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 37200-2025 artfynd.xlsx
+++ b/artfynd/A 37200-2025 artfynd.xlsx
@@ -1225,7 +1225,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128345220</v>
+        <v>128345052</v>
       </c>
       <c r="B7" t="n">
         <v>57689</v>
@@ -1265,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574653</v>
+        <v>574628</v>
       </c>
       <c r="R7" t="n">
-        <v>7088187</v>
+        <v>7088194</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1342,7 +1342,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128345052</v>
+        <v>128345220</v>
       </c>
       <c r="B8" t="n">
         <v>57689</v>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574628</v>
+        <v>574653</v>
       </c>
       <c r="R8" t="n">
-        <v>7088194</v>
+        <v>7088187</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">

--- a/artfynd/A 37200-2025 artfynd.xlsx
+++ b/artfynd/A 37200-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128345174</v>
       </c>
       <c r="B2" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>128345040</v>
       </c>
       <c r="B3" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>128345284</v>
       </c>
       <c r="B4" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>128345094</v>
       </c>
       <c r="B5" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>128345084</v>
       </c>
       <c r="B6" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>128345052</v>
       </c>
       <c r="B7" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>128345220</v>
       </c>
       <c r="B8" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>128344999</v>
       </c>
       <c r="B9" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>128345013</v>
       </c>
       <c r="B10" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>128345290</v>
       </c>
       <c r="B11" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 37200-2025 artfynd.xlsx
+++ b/artfynd/A 37200-2025 artfynd.xlsx
@@ -1225,7 +1225,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128345052</v>
+        <v>128345220</v>
       </c>
       <c r="B7" t="n">
         <v>57716</v>
@@ -1265,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574628</v>
+        <v>574653</v>
       </c>
       <c r="R7" t="n">
-        <v>7088194</v>
+        <v>7088187</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1342,7 +1342,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128345220</v>
+        <v>128345052</v>
       </c>
       <c r="B8" t="n">
         <v>57716</v>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574653</v>
+        <v>574628</v>
       </c>
       <c r="R8" t="n">
-        <v>7088187</v>
+        <v>7088194</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
